--- a/DataTables/Datas/__tables__.xlsx
+++ b/DataTables/Datas/__tables__.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -95,15 +95,6 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>TBUIPanel2</t>
-  </si>
-  <si>
-    <t>DUIPanel2</t>
-  </si>
-  <si>
-    <t>UIPanel2.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1045,8 +1036,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
@@ -1145,23 +1136,6 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
